--- a/docs/edt_entrega_2.xlsx
+++ b/docs/edt_entrega_2.xlsx
@@ -2,14 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoja1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cronograma" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -19,45 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="DD-MM-YYYY"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="FF222222"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF222222"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF222222"/>
-      <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
@@ -71,43 +40,29 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
     <font>
       <color rgb="001F3864"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="007F5000"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="001F3864"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -117,6 +72,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002E75B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F5FA"/>
       </patternFill>
     </fill>
     <fill>
@@ -135,23 +95,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFC1E3D5"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFC1E3D5"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -169,74 +118,66 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -319,44 +260,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -383,15 +324,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -418,7 +358,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -430,142 +369,166 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
@@ -576,2049 +539,2063 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L45"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" bestFit="1" customWidth="1" style="7" min="1" max="1"/>
-    <col width="22" customWidth="1" style="7" min="2" max="2"/>
-    <col width="38" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
-    <col width="22" customWidth="1" style="7" min="4" max="4"/>
-    <col width="18" bestFit="1" customWidth="1" style="7" min="5" max="5"/>
-    <col width="18" bestFit="1" customWidth="1" style="7" min="6" max="6"/>
-    <col width="16" customWidth="1" style="7" min="7" max="10"/>
-    <col width="12" customWidth="1" style="7" min="8" max="8"/>
-    <col width="14" customWidth="1" style="7" min="9" max="9"/>
-    <col width="12" customWidth="1" style="7" min="10" max="10"/>
-    <col width="12" bestFit="1" customWidth="1" style="7" min="11" max="11"/>
-    <col width="50" customWidth="1" style="7" min="12" max="12"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" s="7">
-      <c r="A1" s="14" t="inlineStr">
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Cronograma del Proyecto — Consultorio Digital</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="14" customHeight="1" s="7">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+      <c r="L1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="14" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>ICI-513 Gestión de Proyectos Informáticos · Universidad de Valparaíso · Fecha base: 10-03-2026</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="40" customHeight="1" s="7">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="4" t="n"/>
+      <c r="H2" s="4" t="n"/>
+      <c r="I2" s="4" t="n"/>
+      <c r="J2" s="4" t="n"/>
+      <c r="K2" s="4" t="n"/>
+      <c r="L2" s="4" t="n"/>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>N° EDT</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Etapa</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Nombre de Tarea</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Inicio Planificado</t>
         </is>
       </c>
-      <c r="F3" s="16" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Término Planificado</t>
         </is>
       </c>
-      <c r="G3" s="16" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Dependencia (EDT)</t>
         </is>
       </c>
-      <c r="H3" s="16" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Progreso (%)</t>
         </is>
       </c>
-      <c r="I3" s="16" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>Progreso Real (%)</t>
         </is>
       </c>
-      <c r="J3" s="16" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>Desviación (%)</t>
         </is>
       </c>
-      <c r="K3" s="16" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>Duración (h)</t>
         </is>
       </c>
-      <c r="L3" s="16" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1" s="7">
-      <c r="A4" s="16" t="inlineStr">
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Inicio / Planificación</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>Inicio / Planificación</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
       </c>
-      <c r="E4" s="18" t="n">
+      <c r="E4" s="7" t="n">
         <v>46091</v>
       </c>
-      <c r="F4" s="18" t="n">
+      <c r="F4" s="7" t="n">
         <v>46097</v>
       </c>
-      <c r="G4" s="16" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H4" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="16" t="n">
+      <c r="H4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="L4" s="6" t="inlineStr">
         <is>
           <t>Fase inicial: definición del alcance y planificación del proyecto.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1" s="7">
-      <c r="A5" s="19" t="inlineStr">
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr"/>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr"/>
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>Estudio de Factibilidad</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>Alejandro Dinamarca</t>
         </is>
       </c>
-      <c r="E5" s="21" t="n">
+      <c r="E5" s="10" t="n">
         <v>46091</v>
       </c>
-      <c r="F5" s="21" t="n">
+      <c r="F5" s="10" t="n">
         <v>46092</v>
       </c>
-      <c r="G5" s="19" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H5" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="19" t="n">
+      <c r="H5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L5" s="20" t="inlineStr">
+      <c r="L5" s="9" t="inlineStr">
         <is>
           <t>Análisis de viabilidad técnica, económica y operacional del sistema.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1" s="7">
-      <c r="A6" s="19" t="inlineStr">
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr"/>
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>Caso de Negocio</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>Alexandra Carrasco</t>
         </is>
       </c>
-      <c r="E6" s="21" t="n">
+      <c r="E6" s="13" t="n">
         <v>46093</v>
       </c>
-      <c r="F6" s="21" t="n">
+      <c r="F6" s="13" t="n">
         <v>46094</v>
       </c>
-      <c r="G6" s="19" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="H6" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="19" t="n">
+      <c r="H6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L6" s="20" t="inlineStr">
+      <c r="L6" s="12" t="inlineStr">
         <is>
           <t>Descripción del problema, solución propuesta, beneficios y stakeholders.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1" s="7">
-      <c r="A7" s="19" t="inlineStr">
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr"/>
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>Planificación del Proyecto</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>Ricardo Silva</t>
         </is>
       </c>
-      <c r="E7" s="21" t="n">
+      <c r="E7" s="10" t="n">
         <v>46095</v>
       </c>
-      <c r="F7" s="21" t="n">
+      <c r="F7" s="10" t="n">
         <v>46096</v>
       </c>
-      <c r="G7" s="19" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="H7" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="19" t="n">
+      <c r="H7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L7" s="20" t="inlineStr">
+      <c r="L7" s="9" t="inlineStr">
         <is>
           <t>Definición de hitos, EDT, cronograma y asignación de recursos.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1" s="7">
-      <c r="A8" s="16" t="inlineStr">
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Análisis de Requisitos</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>Análisis de Requisitos</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="7" t="n">
         <v>46097</v>
       </c>
-      <c r="F8" s="18" t="n">
+      <c r="F8" s="7" t="n">
         <v>46103</v>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="H8" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="16" t="n">
+      <c r="H8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="L8" s="6" t="inlineStr">
         <is>
           <t>Levantamiento y documentación de todos los requisitos del sistema.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1" s="7">
-      <c r="A9" s="19" t="inlineStr">
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr"/>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr"/>
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>Levantamiento de Requisitos</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>Lucas Rojas</t>
         </is>
       </c>
-      <c r="E9" s="21" t="n">
+      <c r="E9" s="10" t="n">
         <v>46097</v>
       </c>
-      <c r="F9" s="21" t="n">
+      <c r="F9" s="10" t="n">
         <v>46099</v>
       </c>
-      <c r="G9" s="19" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="H9" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="19" t="n">
+      <c r="H9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L9" s="20" t="inlineStr">
+      <c r="L9" s="9" t="inlineStr">
         <is>
           <t>Entrevistas con stakeholders, casos de uso y requisitos funcionales.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1" s="7">
-      <c r="A10" s="19" t="inlineStr">
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr"/>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr"/>
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>Planificación de Seguridad</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>Allan Gálvez</t>
         </is>
       </c>
-      <c r="E10" s="21" t="n">
+      <c r="E10" s="13" t="n">
         <v>46100</v>
       </c>
-      <c r="F10" s="21" t="n">
+      <c r="F10" s="13" t="n">
         <v>46101</v>
       </c>
-      <c r="G10" s="19" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
       </c>
-      <c r="H10" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="19" t="n">
+      <c r="H10" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L10" s="20" t="inlineStr">
+      <c r="L10" s="12" t="inlineStr">
         <is>
           <t>Definición de políticas de autenticación, autorización y protección de datos.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1" s="7">
-      <c r="A11" s="22" t="inlineStr">
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr"/>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr"/>
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>⬛ Análisis de Requisitos Completado</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr">
+      <c r="D11" s="15" t="inlineStr">
         <is>
           <t>Alejandro Dinamarca</t>
         </is>
       </c>
-      <c r="E11" s="24" t="n">
+      <c r="E11" s="16" t="n">
         <v>46103</v>
       </c>
-      <c r="F11" s="24" t="n">
+      <c r="F11" s="16" t="n">
         <v>46103</v>
       </c>
-      <c r="G11" s="22" t="inlineStr">
+      <c r="G11" s="14" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="H11" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="23" t="inlineStr">
+      <c r="H11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="15" t="inlineStr">
         <is>
           <t>HITO: Revisión y aprobación formal del documento de requisitos.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1" s="7">
-      <c r="A12" s="16" t="inlineStr">
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Diseño</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Diseño</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="7" t="n">
         <v>46104</v>
       </c>
-      <c r="F12" s="18" t="n">
+      <c r="F12" s="7" t="n">
         <v>46110</v>
       </c>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
       </c>
-      <c r="H12" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="16" t="n">
+      <c r="H12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="L12" s="6" t="inlineStr">
         <is>
           <t>Diseño de la arquitectura y prototipos de la solución.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1" s="7">
-      <c r="A13" s="19" t="inlineStr">
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr"/>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr"/>
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>Diseño de Alto Nivel</t>
         </is>
       </c>
-      <c r="D13" s="20" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>Ricardo Silva</t>
         </is>
       </c>
-      <c r="E13" s="21" t="n">
+      <c r="E13" s="10" t="n">
         <v>46104</v>
       </c>
-      <c r="F13" s="21" t="n">
+      <c r="F13" s="10" t="n">
         <v>46105</v>
       </c>
-      <c r="G13" s="19" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
       </c>
-      <c r="H13" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="19" t="n">
+      <c r="H13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L13" s="20" t="inlineStr">
+      <c r="L13" s="9" t="inlineStr">
         <is>
           <t>Definición de la arquitectura general: Django, SQLite, Bootstrap.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1" s="7">
-      <c r="A14" s="19" t="inlineStr">
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr"/>
-      <c r="C14" s="20" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr"/>
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>Prueba de Concepto</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>Alexandra Carrasco</t>
         </is>
       </c>
-      <c r="E14" s="21" t="n">
+      <c r="E14" s="13" t="n">
         <v>46106</v>
       </c>
-      <c r="F14" s="21" t="n">
+      <c r="F14" s="13" t="n">
         <v>46107</v>
       </c>
-      <c r="G14" s="19" t="inlineStr">
+      <c r="G14" s="11" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
       </c>
-      <c r="H14" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="19" t="n">
+      <c r="H14" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L14" s="20" t="inlineStr">
+      <c r="L14" s="12" t="inlineStr">
         <is>
           <t>Prototipo navegable en Figma con flujos principales del paciente y profesional.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1" s="7">
-      <c r="A15" s="19" t="inlineStr">
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr"/>
-      <c r="C15" s="20" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr"/>
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>Diseño Detallado</t>
         </is>
       </c>
-      <c r="D15" s="20" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>Lucas Rojas</t>
         </is>
       </c>
-      <c r="E15" s="21" t="n">
+      <c r="E15" s="10" t="n">
         <v>46108</v>
       </c>
-      <c r="F15" s="21" t="n">
+      <c r="F15" s="10" t="n">
         <v>46108</v>
       </c>
-      <c r="G15" s="19" t="inlineStr">
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
       </c>
-      <c r="H15" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="19" t="n">
+      <c r="H15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L15" s="20" t="inlineStr">
+      <c r="L15" s="9" t="inlineStr">
         <is>
           <t>Diseño detallado de módulos, vistas, endpoints y modelo de datos.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1" s="7">
-      <c r="A16" s="19" t="inlineStr">
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
       </c>
-      <c r="B16" s="20" t="inlineStr"/>
-      <c r="C16" s="20" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr"/>
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>Especificación Técnica</t>
         </is>
       </c>
-      <c r="D16" s="20" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>Allan Gálvez</t>
         </is>
       </c>
-      <c r="E16" s="21" t="n">
+      <c r="E16" s="13" t="n">
         <v>46109</v>
       </c>
-      <c r="F16" s="21" t="n">
+      <c r="F16" s="13" t="n">
         <v>46109</v>
       </c>
-      <c r="G16" s="19" t="inlineStr">
+      <c r="G16" s="11" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
       </c>
-      <c r="H16" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="19" t="n">
+      <c r="H16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L16" s="20" t="inlineStr">
+      <c r="L16" s="12" t="inlineStr">
         <is>
           <t>Documentación técnica de URLs, modelos y especificaciones de seguridad.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1" s="7">
-      <c r="A17" s="22" t="inlineStr">
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
       </c>
-      <c r="B17" s="23" t="inlineStr"/>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr"/>
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <t>⬛ Diseño Completado</t>
         </is>
       </c>
-      <c r="D17" s="23" t="inlineStr">
+      <c r="D17" s="15" t="inlineStr">
         <is>
           <t>Alejandro Dinamarca</t>
         </is>
       </c>
-      <c r="E17" s="24" t="n">
+      <c r="E17" s="16" t="n">
         <v>46110</v>
       </c>
-      <c r="F17" s="24" t="n">
+      <c r="F17" s="16" t="n">
         <v>46110</v>
       </c>
-      <c r="G17" s="22" t="inlineStr">
+      <c r="G17" s="14" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
       </c>
-      <c r="H17" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="23" t="inlineStr">
+      <c r="H17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="15" t="inlineStr">
         <is>
           <t>HITO: Revisión y aprobación formal del diseño.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1" s="7">
-      <c r="A18" s="16" t="inlineStr">
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>Desarrollo</t>
         </is>
       </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>Desarrollo</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
       </c>
-      <c r="E18" s="18" t="n">
+      <c r="E18" s="7" t="n">
         <v>46111</v>
       </c>
-      <c r="F18" s="18" t="n">
+      <c r="F18" s="7" t="n">
         <v>46132</v>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
       </c>
-      <c r="H18" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="16" t="n">
+      <c r="H18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="5" t="n">
         <v>88</v>
       </c>
-      <c r="L18" s="17" t="inlineStr">
+      <c r="L18" s="6" t="inlineStr">
         <is>
           <t>Implementación del sistema según el diseño aprobado.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1" s="7">
-      <c r="A19" s="19" t="inlineStr">
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="B19" s="20" t="inlineStr"/>
-      <c r="C19" s="20" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr"/>
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>Creación de Ambientes</t>
         </is>
       </c>
-      <c r="D19" s="20" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>Allan Gálvez</t>
         </is>
       </c>
-      <c r="E19" s="21" t="n">
+      <c r="E19" s="10" t="n">
         <v>46111</v>
       </c>
-      <c r="F19" s="21" t="n">
+      <c r="F19" s="10" t="n">
         <v>46114</v>
       </c>
-      <c r="G19" s="19" t="inlineStr">
+      <c r="G19" s="8" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
       </c>
-      <c r="H19" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="19" t="n">
+      <c r="H19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="L19" s="20" t="inlineStr">
+      <c r="L19" s="9" t="inlineStr">
         <is>
           <t>Configuración de entornos de desarrollo local y producción con Django.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1" s="7">
-      <c r="A20" s="19" t="inlineStr">
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
       </c>
-      <c r="B20" s="20" t="inlineStr"/>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr"/>
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>Creación de Base de Datos</t>
         </is>
       </c>
-      <c r="D20" s="20" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>Alejandro Dinamarca</t>
         </is>
       </c>
-      <c r="E20" s="21" t="n">
+      <c r="E20" s="13" t="n">
         <v>46115</v>
       </c>
-      <c r="F20" s="21" t="n">
+      <c r="F20" s="13" t="n">
         <v>46115</v>
       </c>
-      <c r="G20" s="19" t="inlineStr">
+      <c r="G20" s="11" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="H20" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="19" t="n">
+      <c r="H20" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L20" s="20" t="inlineStr">
+      <c r="L20" s="12" t="inlineStr">
         <is>
           <t>Creación y migración del esquema SQLite; carga de datos geográficos.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1" s="7">
-      <c r="A21" s="19" t="inlineStr">
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
       </c>
-      <c r="B21" s="20" t="inlineStr"/>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr"/>
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>Configuraciones Adicionales</t>
         </is>
       </c>
-      <c r="D21" s="20" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>Allan Gálvez</t>
         </is>
       </c>
-      <c r="E21" s="21" t="n">
+      <c r="E21" s="10" t="n">
         <v>46116</v>
       </c>
-      <c r="F21" s="21" t="n">
+      <c r="F21" s="10" t="n">
         <v>46116</v>
       </c>
-      <c r="G21" s="19" t="inlineStr">
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
       </c>
-      <c r="H21" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="19" t="n">
+      <c r="H21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L21" s="20" t="inlineStr">
+      <c r="L21" s="9" t="inlineStr">
         <is>
           <t>Configuración de variables de entorno, CORS, autenticación y servicios.</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1" s="7">
-      <c r="A22" s="19" t="inlineStr">
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
       </c>
-      <c r="B22" s="20" t="inlineStr"/>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr"/>
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>Maquetación de Pantallas</t>
         </is>
       </c>
-      <c r="D22" s="20" t="inlineStr">
+      <c r="D22" s="12" t="inlineStr">
         <is>
           <t>Alexandra Carrasco</t>
         </is>
       </c>
-      <c r="E22" s="21" t="n">
+      <c r="E22" s="13" t="n">
         <v>46111</v>
       </c>
-      <c r="F22" s="21" t="n">
+      <c r="F22" s="13" t="n">
         <v>46113</v>
       </c>
-      <c r="G22" s="19" t="inlineStr">
+      <c r="G22" s="11" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
       </c>
-      <c r="H22" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="19" t="n">
+      <c r="H22" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L22" s="20" t="inlineStr">
+      <c r="L22" s="12" t="inlineStr">
         <is>
           <t>Maquetación de templates HTML con Bootstrap según prototipos aprobados.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1" s="7">
-      <c r="A23" s="19" t="inlineStr">
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="B23" s="20" t="inlineStr"/>
-      <c r="C23" s="20" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr"/>
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>Desarrollo Frontend (Templates)</t>
         </is>
       </c>
-      <c r="D23" s="20" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>Lucas Rojas</t>
         </is>
       </c>
-      <c r="E23" s="21" t="n">
+      <c r="E23" s="10" t="n">
         <v>46117</v>
       </c>
-      <c r="F23" s="21" t="n">
+      <c r="F23" s="10" t="n">
         <v>46118</v>
       </c>
-      <c r="G23" s="19" t="inlineStr">
+      <c r="G23" s="8" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
       </c>
-      <c r="H23" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="19" t="n">
+      <c r="H23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L23" s="20" t="inlineStr">
+      <c r="L23" s="9" t="inlineStr">
         <is>
           <t>Implementación de templates Django y lógica JS para flujos del usuario.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="30" customHeight="1" s="7">
-      <c r="A24" s="19" t="inlineStr">
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
       </c>
-      <c r="B24" s="20" t="inlineStr"/>
-      <c r="C24" s="20" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr"/>
+      <c r="C24" s="12" t="inlineStr">
         <is>
           <t>Desarrollo Backend</t>
         </is>
       </c>
-      <c r="D24" s="20" t="inlineStr">
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>Ricardo Silva</t>
         </is>
       </c>
-      <c r="E24" s="21" t="n">
+      <c r="E24" s="13" t="n">
         <v>46119</v>
       </c>
-      <c r="F24" s="21" t="n">
+      <c r="F24" s="13" t="n">
         <v>46124</v>
       </c>
-      <c r="G24" s="19" t="inlineStr">
+      <c r="G24" s="11" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="H24" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="19" t="n">
+      <c r="H24" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="11" t="n">
         <v>24</v>
       </c>
-      <c r="L24" s="20" t="inlineStr">
+      <c r="L24" s="12" t="inlineStr">
         <is>
           <t>Desarrollo de vistas, modelos y lógica de negocio con Django.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="30" customHeight="1" s="7">
-      <c r="A25" s="19" t="inlineStr">
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
       </c>
-      <c r="B25" s="20" t="inlineStr"/>
-      <c r="C25" s="20" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr"/>
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>Integración Frontend-Backend</t>
         </is>
       </c>
-      <c r="D25" s="20" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>Lucas Rojas</t>
         </is>
       </c>
-      <c r="E25" s="21" t="n">
+      <c r="E25" s="10" t="n">
         <v>46125</v>
       </c>
-      <c r="F25" s="21" t="n">
+      <c r="F25" s="10" t="n">
         <v>46127</v>
       </c>
-      <c r="G25" s="19" t="inlineStr">
+      <c r="G25" s="8" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
       </c>
-      <c r="H25" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="19" t="n">
+      <c r="H25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L25" s="20" t="inlineStr">
+      <c r="L25" s="9" t="inlineStr">
         <is>
           <t>Integración de templates con vistas Django; ajustes de UX y validación.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="30" customHeight="1" s="7">
-      <c r="A26" s="19" t="inlineStr">
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
       </c>
-      <c r="B26" s="20" t="inlineStr"/>
-      <c r="C26" s="20" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr"/>
+      <c r="C26" s="12" t="inlineStr">
         <is>
           <t>Planificación de la Calidad</t>
         </is>
       </c>
-      <c r="D26" s="20" t="inlineStr">
+      <c r="D26" s="12" t="inlineStr">
         <is>
           <t>Alexandra Carrasco</t>
         </is>
       </c>
-      <c r="E26" s="21" t="n">
+      <c r="E26" s="13" t="n">
         <v>46128</v>
       </c>
-      <c r="F26" s="21" t="n">
+      <c r="F26" s="13" t="n">
         <v>46129</v>
       </c>
-      <c r="G26" s="19" t="inlineStr">
+      <c r="G26" s="11" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
       </c>
-      <c r="H26" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="19" t="n">
+      <c r="H26" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L26" s="20" t="inlineStr">
+      <c r="L26" s="12" t="inlineStr">
         <is>
           <t>Definición de criterios de calidad, métricas y plan de pruebas.</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="30" customHeight="1" s="7">
-      <c r="A27" s="16" t="inlineStr">
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B27" s="17" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>Aseguramiento de Calidad</t>
         </is>
       </c>
-      <c r="C27" s="17" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>Aseguramiento de Calidad</t>
         </is>
       </c>
-      <c r="D27" s="17" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
       </c>
-      <c r="E27" s="18" t="n">
+      <c r="E27" s="7" t="n">
         <v>46130</v>
       </c>
-      <c r="F27" s="18" t="n">
+      <c r="F27" s="7" t="n">
         <v>46148</v>
       </c>
-      <c r="G27" s="16" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
       </c>
-      <c r="H27" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="16" t="n">
+      <c r="H27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="5" t="n">
         <v>56</v>
       </c>
-      <c r="L27" s="17" t="inlineStr">
+      <c r="L27" s="6" t="inlineStr">
         <is>
           <t>Verificación y validación del sistema construido.</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="30" customHeight="1" s="7">
-      <c r="A28" s="19" t="inlineStr">
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
       </c>
-      <c r="B28" s="20" t="inlineStr"/>
-      <c r="C28" s="20" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr"/>
+      <c r="C28" s="12" t="inlineStr">
         <is>
           <t>Prueba Unitaria</t>
         </is>
       </c>
-      <c r="D28" s="20" t="inlineStr">
+      <c r="D28" s="12" t="inlineStr">
         <is>
           <t>Ricardo Silva</t>
         </is>
       </c>
-      <c r="E28" s="21" t="n">
+      <c r="E28" s="13" t="n">
         <v>46130</v>
       </c>
-      <c r="F28" s="21" t="n">
+      <c r="F28" s="13" t="n">
         <v>46132</v>
       </c>
-      <c r="G28" s="19" t="inlineStr">
+      <c r="G28" s="11" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
       </c>
-      <c r="H28" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" s="19" t="n">
+      <c r="H28" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L28" s="20" t="inlineStr">
+      <c r="L28" s="12" t="inlineStr">
         <is>
           <t>Pruebas de funciones individuales con pytest y Django TestCase.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="30" customHeight="1" s="7">
-      <c r="A29" s="19" t="inlineStr">
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>5.2</t>
         </is>
       </c>
-      <c r="B29" s="20" t="inlineStr"/>
-      <c r="C29" s="20" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr"/>
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>Prueba Funcional</t>
         </is>
       </c>
-      <c r="D29" s="20" t="inlineStr">
+      <c r="D29" s="9" t="inlineStr">
         <is>
           <t>Alexandra Carrasco</t>
         </is>
       </c>
-      <c r="E29" s="21" t="n">
+      <c r="E29" s="10" t="n">
         <v>46133</v>
       </c>
-      <c r="F29" s="21" t="n">
+      <c r="F29" s="10" t="n">
         <v>46134</v>
       </c>
-      <c r="G29" s="19" t="inlineStr">
+      <c r="G29" s="8" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
       </c>
-      <c r="H29" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="19" t="n">
+      <c r="H29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L29" s="20" t="inlineStr">
+      <c r="L29" s="9" t="inlineStr">
         <is>
           <t>Pruebas de flujos completos según criterios de aceptación.</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="30" customHeight="1" s="7">
-      <c r="A30" s="19" t="inlineStr">
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
       </c>
-      <c r="B30" s="20" t="inlineStr"/>
-      <c r="C30" s="20" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr"/>
+      <c r="C30" s="12" t="inlineStr">
         <is>
           <t>Prueba de Integración</t>
         </is>
       </c>
-      <c r="D30" s="20" t="inlineStr">
+      <c r="D30" s="12" t="inlineStr">
         <is>
           <t>Alejandro Dinamarca</t>
         </is>
       </c>
-      <c r="E30" s="21" t="n">
+      <c r="E30" s="13" t="n">
         <v>46135</v>
       </c>
-      <c r="F30" s="21" t="n">
+      <c r="F30" s="13" t="n">
         <v>46140</v>
       </c>
-      <c r="G30" s="19" t="inlineStr">
+      <c r="G30" s="11" t="inlineStr">
         <is>
           <t>5.2</t>
         </is>
       </c>
-      <c r="H30" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="19" t="n">
+      <c r="H30" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="11" t="n">
         <v>24</v>
       </c>
-      <c r="L30" s="20" t="inlineStr">
+      <c r="L30" s="12" t="inlineStr">
         <is>
           <t>Pruebas de integración entre vistas, modelos y base de datos.</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="30" customHeight="1" s="7">
-      <c r="A31" s="19" t="inlineStr">
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>5.4</t>
         </is>
       </c>
-      <c r="B31" s="20" t="inlineStr"/>
-      <c r="C31" s="20" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr"/>
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>Prueba de Regresión</t>
         </is>
       </c>
-      <c r="D31" s="20" t="inlineStr">
+      <c r="D31" s="9" t="inlineStr">
         <is>
           <t>Lucas Rojas</t>
         </is>
       </c>
-      <c r="E31" s="21" t="n">
+      <c r="E31" s="10" t="n">
         <v>46141</v>
       </c>
-      <c r="F31" s="21" t="n">
+      <c r="F31" s="10" t="n">
         <v>46142</v>
       </c>
-      <c r="G31" s="19" t="inlineStr">
+      <c r="G31" s="8" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
       </c>
-      <c r="H31" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="19" t="n">
+      <c r="H31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L31" s="20" t="inlineStr">
+      <c r="L31" s="9" t="inlineStr">
         <is>
           <t>Verificación de que cambios no rompan funcionalidades previas.</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="30" customHeight="1" s="7">
-      <c r="A32" s="19" t="inlineStr">
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>5.5</t>
         </is>
       </c>
-      <c r="B32" s="20" t="inlineStr"/>
-      <c r="C32" s="20" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr"/>
+      <c r="C32" s="12" t="inlineStr">
         <is>
           <t>Prueba de Sistema</t>
         </is>
       </c>
-      <c r="D32" s="20" t="inlineStr">
+      <c r="D32" s="12" t="inlineStr">
         <is>
           <t>Allan Gálvez</t>
         </is>
       </c>
-      <c r="E32" s="21" t="n">
+      <c r="E32" s="13" t="n">
         <v>46143</v>
       </c>
-      <c r="F32" s="21" t="n">
+      <c r="F32" s="13" t="n">
         <v>46144</v>
       </c>
-      <c r="G32" s="19" t="inlineStr">
+      <c r="G32" s="11" t="inlineStr">
         <is>
           <t>5.4</t>
         </is>
       </c>
-      <c r="H32" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="19" t="n">
+      <c r="H32" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L32" s="20" t="inlineStr">
+      <c r="L32" s="12" t="inlineStr">
         <is>
           <t>Prueba del sistema completo en ambiente de staging.</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="30" customHeight="1" s="7">
-      <c r="A33" s="19" t="inlineStr">
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
       </c>
-      <c r="B33" s="20" t="inlineStr"/>
-      <c r="C33" s="20" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr"/>
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>Prueba de Aceptación de Usuario</t>
         </is>
       </c>
-      <c r="D33" s="20" t="inlineStr">
+      <c r="D33" s="9" t="inlineStr">
         <is>
           <t>Ricardo Silva</t>
         </is>
       </c>
-      <c r="E33" s="21" t="n">
+      <c r="E33" s="10" t="n">
         <v>46145</v>
       </c>
-      <c r="F33" s="21" t="n">
+      <c r="F33" s="10" t="n">
         <v>46147</v>
       </c>
-      <c r="G33" s="19" t="inlineStr">
+      <c r="G33" s="8" t="inlineStr">
         <is>
           <t>5.5</t>
         </is>
       </c>
-      <c r="H33" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" s="19" t="n">
+      <c r="H33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L33" s="20" t="inlineStr">
+      <c r="L33" s="9" t="inlineStr">
         <is>
           <t>Validación por parte de usuarios representativos del sistema.</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="30" customHeight="1" s="7">
-      <c r="A34" s="22" t="inlineStr">
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="14" t="inlineStr">
         <is>
           <t>5.7</t>
         </is>
       </c>
-      <c r="B34" s="23" t="inlineStr"/>
-      <c r="C34" s="23" t="inlineStr">
+      <c r="B34" s="15" t="inlineStr"/>
+      <c r="C34" s="15" t="inlineStr">
         <is>
           <t>⬛ Sistema Aprobado para Despliegue</t>
         </is>
       </c>
-      <c r="D34" s="23" t="inlineStr">
+      <c r="D34" s="15" t="inlineStr">
         <is>
           <t>Alejandro Dinamarca</t>
         </is>
       </c>
-      <c r="E34" s="24" t="n">
+      <c r="E34" s="16" t="n">
         <v>46148</v>
       </c>
-      <c r="F34" s="24" t="n">
+      <c r="F34" s="16" t="n">
         <v>46148</v>
       </c>
-      <c r="G34" s="22" t="inlineStr">
+      <c r="G34" s="14" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
       </c>
-      <c r="H34" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="23" t="inlineStr">
+      <c r="H34" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="15" t="inlineStr">
         <is>
           <t>HITO: Sistema validado y autorizado para pasar a producción.</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="30" customHeight="1" s="7">
-      <c r="A35" s="16" t="inlineStr">
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B35" s="17" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="C35" s="17" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="D35" s="17" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
       </c>
-      <c r="E35" s="18" t="n">
+      <c r="E35" s="7" t="n">
         <v>46149</v>
       </c>
-      <c r="F35" s="18" t="n">
+      <c r="F35" s="7" t="n">
         <v>46157</v>
       </c>
-      <c r="G35" s="16" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>5.7</t>
         </is>
       </c>
-      <c r="H35" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="16" t="n">
+      <c r="H35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="L35" s="17" t="inlineStr">
+      <c r="L35" s="6" t="inlineStr">
         <is>
           <t>Despliegue y puesta en marcha del sistema en producción.</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="30" customHeight="1" s="7">
-      <c r="A36" s="19" t="inlineStr">
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="11" t="inlineStr">
         <is>
           <t>6.1</t>
         </is>
       </c>
-      <c r="B36" s="20" t="inlineStr"/>
-      <c r="C36" s="20" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr"/>
+      <c r="C36" s="12" t="inlineStr">
         <is>
           <t>Despliegue en Producción</t>
         </is>
       </c>
-      <c r="D36" s="20" t="inlineStr">
+      <c r="D36" s="12" t="inlineStr">
         <is>
           <t>Alejandro Dinamarca</t>
         </is>
       </c>
-      <c r="E36" s="21" t="n">
+      <c r="E36" s="13" t="n">
         <v>46149</v>
       </c>
-      <c r="F36" s="21" t="n">
+      <c r="F36" s="13" t="n">
         <v>46150</v>
       </c>
-      <c r="G36" s="19" t="inlineStr">
+      <c r="G36" s="11" t="inlineStr">
         <is>
           <t>5.7</t>
         </is>
       </c>
-      <c r="H36" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" s="19" t="n">
+      <c r="H36" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L36" s="20" t="inlineStr">
+      <c r="L36" s="12" t="inlineStr">
         <is>
           <t>Despliegue en servidor de producción con configuración final.</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="30" customHeight="1" s="7">
-      <c r="A37" s="19" t="inlineStr">
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
       </c>
-      <c r="B37" s="20" t="inlineStr"/>
-      <c r="C37" s="20" t="inlineStr">
+      <c r="B37" s="9" t="inlineStr"/>
+      <c r="C37" s="9" t="inlineStr">
         <is>
           <t>Capacitación a Usuarios</t>
         </is>
       </c>
-      <c r="D37" s="20" t="inlineStr">
+      <c r="D37" s="9" t="inlineStr">
         <is>
           <t>Alexandra Carrasco</t>
         </is>
       </c>
-      <c r="E37" s="21" t="n">
+      <c r="E37" s="10" t="n">
         <v>46151</v>
       </c>
-      <c r="F37" s="21" t="n">
+      <c r="F37" s="10" t="n">
         <v>46155</v>
       </c>
-      <c r="G37" s="19" t="inlineStr">
+      <c r="G37" s="8" t="inlineStr">
         <is>
           <t>6.1</t>
         </is>
       </c>
-      <c r="H37" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" s="19" t="n">
+      <c r="H37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="L37" s="20" t="inlineStr">
+      <c r="L37" s="9" t="inlineStr">
         <is>
           <t>Capacitación a pacientes de prueba y personal administrativo.</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="30" customHeight="1" s="7">
-      <c r="A38" s="19" t="inlineStr">
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>6.3</t>
         </is>
       </c>
-      <c r="B38" s="20" t="inlineStr"/>
-      <c r="C38" s="20" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr"/>
+      <c r="C38" s="12" t="inlineStr">
         <is>
           <t>Soporte Post-Despliegue</t>
         </is>
       </c>
-      <c r="D38" s="20" t="inlineStr">
+      <c r="D38" s="12" t="inlineStr">
         <is>
           <t>Lucas Rojas</t>
         </is>
       </c>
-      <c r="E38" s="21" t="n">
+      <c r="E38" s="13" t="n">
         <v>46155</v>
       </c>
-      <c r="F38" s="21" t="n">
+      <c r="F38" s="13" t="n">
         <v>46156</v>
       </c>
-      <c r="G38" s="19" t="inlineStr">
+      <c r="G38" s="11" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
       </c>
-      <c r="H38" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" s="19" t="n">
+      <c r="H38" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L38" s="20" t="inlineStr">
+      <c r="L38" s="12" t="inlineStr">
         <is>
           <t>Soporte post-despliegue y corrección de incidencias iniciales.</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="30" customHeight="1" s="7">
-      <c r="A39" s="16" t="inlineStr">
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B39" s="17" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>Operaciones</t>
         </is>
       </c>
-      <c r="C39" s="17" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>Operaciones</t>
         </is>
       </c>
-      <c r="D39" s="17" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
       </c>
-      <c r="E39" s="18" t="n">
+      <c r="E39" s="7" t="n">
         <v>46157</v>
       </c>
-      <c r="F39" s="18" t="n">
+      <c r="F39" s="7" t="n">
         <v>46163</v>
       </c>
-      <c r="G39" s="16" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>6.3</t>
         </is>
       </c>
-      <c r="H39" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" s="16" t="n">
+      <c r="H39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="L39" s="17" t="inlineStr">
+      <c r="L39" s="6" t="inlineStr">
         <is>
           <t>Operación controlada del sistema antes del cierre formal.</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="30" customHeight="1" s="7">
-      <c r="A40" s="19" t="inlineStr">
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="B40" s="20" t="inlineStr"/>
-      <c r="C40" s="20" t="inlineStr">
+      <c r="B40" s="12" t="inlineStr"/>
+      <c r="C40" s="12" t="inlineStr">
         <is>
           <t>Marcha Blanca</t>
         </is>
       </c>
-      <c r="D40" s="20" t="inlineStr">
+      <c r="D40" s="12" t="inlineStr">
         <is>
           <t>Allan Gálvez</t>
         </is>
       </c>
-      <c r="E40" s="21" t="n">
+      <c r="E40" s="13" t="n">
         <v>46157</v>
       </c>
-      <c r="F40" s="21" t="n">
+      <c r="F40" s="13" t="n">
         <v>46161</v>
       </c>
-      <c r="G40" s="19" t="inlineStr">
+      <c r="G40" s="11" t="inlineStr">
         <is>
           <t>6.1</t>
         </is>
       </c>
-      <c r="H40" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" s="19" t="n">
+      <c r="H40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="L40" s="20" t="inlineStr">
+      <c r="L40" s="12" t="inlineStr">
         <is>
           <t>Período de operación supervisada para detectar errores en producción.</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="30" customHeight="1" s="7">
-      <c r="A41" s="19" t="inlineStr">
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>7.2</t>
         </is>
       </c>
-      <c r="B41" s="20" t="inlineStr"/>
-      <c r="C41" s="20" t="inlineStr">
+      <c r="B41" s="9" t="inlineStr"/>
+      <c r="C41" s="9" t="inlineStr">
         <is>
           <t>Corrección de Incidencias</t>
         </is>
       </c>
-      <c r="D41" s="20" t="inlineStr">
+      <c r="D41" s="9" t="inlineStr">
         <is>
           <t>Ricardo Silva</t>
         </is>
       </c>
-      <c r="E41" s="21" t="n">
+      <c r="E41" s="10" t="n">
         <v>46161</v>
       </c>
-      <c r="F41" s="21" t="n">
+      <c r="F41" s="10" t="n">
         <v>46163</v>
       </c>
-      <c r="G41" s="19" t="inlineStr">
+      <c r="G41" s="8" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="H41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="19" t="n">
+      <c r="H41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L41" s="20" t="inlineStr">
+      <c r="L41" s="9" t="inlineStr">
         <is>
           <t>Resolución de errores detectados durante la marcha blanca.</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="30" customHeight="1" s="7">
-      <c r="A42" s="16" t="inlineStr">
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B42" s="17" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="C42" s="17" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="D42" s="17" t="inlineStr">
+      <c r="D42" s="6" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
       </c>
-      <c r="E42" s="18" t="n">
+      <c r="E42" s="7" t="n">
         <v>46164</v>
       </c>
-      <c r="F42" s="18" t="n">
+      <c r="F42" s="7" t="n">
         <v>46169</v>
       </c>
-      <c r="G42" s="16" t="inlineStr">
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>7.2</t>
         </is>
       </c>
-      <c r="H42" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" s="16" t="n">
+      <c r="H42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="L42" s="17" t="inlineStr">
+      <c r="L42" s="6" t="inlineStr">
         <is>
           <t>Cierre formal del proyecto y entrega de documentación.</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="30" customHeight="1" s="7">
-      <c r="A43" s="19" t="inlineStr">
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="B43" s="20" t="inlineStr"/>
-      <c r="C43" s="20" t="inlineStr">
+      <c r="B43" s="9" t="inlineStr"/>
+      <c r="C43" s="9" t="inlineStr">
         <is>
           <t>Documentación Final</t>
         </is>
       </c>
-      <c r="D43" s="20" t="inlineStr">
+      <c r="D43" s="9" t="inlineStr">
         <is>
           <t>Ricardo Silva</t>
         </is>
       </c>
-      <c r="E43" s="21" t="n">
+      <c r="E43" s="10" t="n">
         <v>46164</v>
       </c>
-      <c r="F43" s="21" t="n">
+      <c r="F43" s="10" t="n">
         <v>46166</v>
       </c>
-      <c r="G43" s="19" t="inlineStr">
+      <c r="G43" s="8" t="inlineStr">
         <is>
           <t>7.2</t>
         </is>
       </c>
-      <c r="H43" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" s="19" t="n">
+      <c r="H43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="L43" s="20" t="inlineStr">
+      <c r="L43" s="9" t="inlineStr">
         <is>
           <t>Manual de usuario, manual técnico y documentación del código.</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="30" customHeight="1" s="7">
-      <c r="A44" s="22" t="inlineStr">
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="14" t="inlineStr">
         <is>
           <t>8.2</t>
         </is>
       </c>
-      <c r="B44" s="23" t="inlineStr"/>
-      <c r="C44" s="23" t="inlineStr">
+      <c r="B44" s="15" t="inlineStr"/>
+      <c r="C44" s="15" t="inlineStr">
         <is>
           <t>⬛ Cierre Formal del Proyecto</t>
         </is>
       </c>
-      <c r="D44" s="23" t="inlineStr">
+      <c r="D44" s="15" t="inlineStr">
         <is>
           <t>Alejandro Dinamarca</t>
         </is>
       </c>
-      <c r="E44" s="24" t="n">
+      <c r="E44" s="16" t="n">
         <v>46169</v>
       </c>
-      <c r="F44" s="24" t="n">
+      <c r="F44" s="16" t="n">
         <v>46169</v>
       </c>
-      <c r="G44" s="22" t="inlineStr">
+      <c r="G44" s="14" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="H44" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="23" t="inlineStr">
+      <c r="H44" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="15" t="inlineStr">
         <is>
           <t>HITO: Acta de cierre, lecciones aprendidas y entrega al cliente.</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="30" customHeight="1" s="7">
-      <c r="A45" s="25" t="n"/>
-      <c r="B45" s="25" t="n"/>
-      <c r="C45" s="25" t="n"/>
-      <c r="D45" s="25" t="n"/>
-      <c r="E45" s="25" t="n"/>
-      <c r="F45" s="25" t="n"/>
-      <c r="G45" s="26" t="inlineStr">
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="17" t="n"/>
+      <c r="B45" s="17" t="n"/>
+      <c r="C45" s="17" t="n"/>
+      <c r="D45" s="17" t="n"/>
+      <c r="E45" s="17" t="n"/>
+      <c r="F45" s="17" t="n"/>
+      <c r="G45" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="H45" s="25" t="n"/>
-      <c r="I45" s="25" t="n"/>
-      <c r="J45" s="25" t="n"/>
-      <c r="K45" s="26" t="n">
+      <c r="H45" s="17" t="n"/>
+      <c r="I45" s="17" t="n"/>
+      <c r="J45" s="17" t="n"/>
+      <c r="K45" s="18" t="n">
         <v>552</v>
       </c>
-      <c r="L45" s="25" t="n"/>
+      <c r="L45" s="17" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B2:C2"/>
+  <mergeCells count="2">
     <mergeCell ref="A2:L2"/>
-    <mergeCell ref="B25:C25"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/edt_entrega_2.xlsx
+++ b/docs/edt_entrega_2.xlsx
@@ -992,7 +992,7 @@
       <c r="B11" s="15" t="inlineStr"/>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>⬛ Análisis de Requisitos Completado</t>
+          <t>Análisis de Requisitos Completado</t>
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr">
@@ -1272,7 +1272,7 @@
       <c r="B17" s="15" t="inlineStr"/>
       <c r="C17" s="15" t="inlineStr">
         <is>
-          <t>⬛ Diseño Completado</t>
+          <t>Diseño Completado</t>
         </is>
       </c>
       <c r="D17" s="15" t="inlineStr">
@@ -2062,7 +2062,7 @@
       <c r="B34" s="15" t="inlineStr"/>
       <c r="C34" s="15" t="inlineStr">
         <is>
-          <t>⬛ Sistema Aprobado para Despliegue</t>
+          <t>Sistema Aprobado para Despliegue</t>
         </is>
       </c>
       <c r="D34" s="15" t="inlineStr">
@@ -2534,7 +2534,7 @@
       <c r="B44" s="15" t="inlineStr"/>
       <c r="C44" s="15" t="inlineStr">
         <is>
-          <t>⬛ Cierre Formal del Proyecto</t>
+          <t>Cierre Formal del Proyecto</t>
         </is>
       </c>
       <c r="D44" s="15" t="inlineStr">

--- a/docs/edt_entrega_2.xlsx
+++ b/docs/edt_entrega_2.xlsx
@@ -16,9 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="DD-MM-YYYY"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="DD-MM-YYYY"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -121,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -137,7 +136,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -146,7 +145,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -155,7 +154,7 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -164,13 +163,25 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -561,35 +572,13 @@
           <t>Cronograma del Proyecto — Consultorio Digital</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
     </row>
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>ICI-513 Gestión de Proyectos Informáticos · Universidad de Valparaíso · Fecha base: 10-03-2026</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="n"/>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="n"/>
-      <c r="E2" s="4" t="n"/>
-      <c r="F2" s="4" t="n"/>
-      <c r="G2" s="4" t="n"/>
-      <c r="H2" s="4" t="n"/>
-      <c r="I2" s="4" t="n"/>
-      <c r="J2" s="4" t="n"/>
-      <c r="K2" s="4" t="n"/>
-      <c r="L2" s="4" t="n"/>
+          <t>ICI-513 Gestión de Proyectos Informáticos · Universidad de Valparaíso · Fecha base: 10-03-2026 · Dedicación part-time: ~2 h/día por persona responsable</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="40" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
@@ -674,11 +663,11 @@
           <t>Todos</t>
         </is>
       </c>
-      <c r="E4" s="7" t="n">
+      <c r="E4" s="19" t="n">
         <v>46091</v>
       </c>
-      <c r="F4" s="7" t="n">
-        <v>46097</v>
+      <c r="F4" s="19" t="n">
+        <v>46103</v>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
@@ -720,11 +709,11 @@
           <t>Alejandro Dinamarca</t>
         </is>
       </c>
-      <c r="E5" s="10" t="n">
+      <c r="E5" s="20" t="n">
         <v>46091</v>
       </c>
-      <c r="F5" s="10" t="n">
-        <v>46092</v>
+      <c r="F5" s="20" t="n">
+        <v>46094</v>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
@@ -766,11 +755,11 @@
           <t>Alexandra Carrasco</t>
         </is>
       </c>
-      <c r="E6" s="13" t="n">
-        <v>46093</v>
-      </c>
-      <c r="F6" s="13" t="n">
-        <v>46094</v>
+      <c r="E6" s="21" t="n">
+        <v>46095</v>
+      </c>
+      <c r="F6" s="21" t="n">
+        <v>46098</v>
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
@@ -812,11 +801,11 @@
           <t>Ricardo Silva</t>
         </is>
       </c>
-      <c r="E7" s="10" t="n">
-        <v>46095</v>
-      </c>
-      <c r="F7" s="10" t="n">
-        <v>46096</v>
+      <c r="E7" s="20" t="n">
+        <v>46099</v>
+      </c>
+      <c r="F7" s="20" t="n">
+        <v>46103</v>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
@@ -862,11 +851,11 @@
           <t>Todos</t>
         </is>
       </c>
-      <c r="E8" s="7" t="n">
-        <v>46097</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>46103</v>
+      <c r="E8" s="19" t="n">
+        <v>46104</v>
+      </c>
+      <c r="F8" s="19" t="n">
+        <v>46118</v>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
@@ -908,11 +897,11 @@
           <t>Lucas Rojas</t>
         </is>
       </c>
-      <c r="E9" s="10" t="n">
-        <v>46097</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>46099</v>
+      <c r="E9" s="20" t="n">
+        <v>46104</v>
+      </c>
+      <c r="F9" s="20" t="n">
+        <v>46110</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -954,11 +943,11 @@
           <t>Allan Gálvez</t>
         </is>
       </c>
-      <c r="E10" s="13" t="n">
-        <v>46100</v>
-      </c>
-      <c r="F10" s="13" t="n">
-        <v>46101</v>
+      <c r="E10" s="21" t="n">
+        <v>46111</v>
+      </c>
+      <c r="F10" s="21" t="n">
+        <v>46115</v>
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
@@ -1000,11 +989,11 @@
           <t>Alejandro Dinamarca</t>
         </is>
       </c>
-      <c r="E11" s="16" t="n">
-        <v>46103</v>
-      </c>
-      <c r="F11" s="16" t="n">
-        <v>46103</v>
+      <c r="E11" s="22" t="n">
+        <v>46118</v>
+      </c>
+      <c r="F11" s="22" t="n">
+        <v>46118</v>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
@@ -1050,11 +1039,11 @@
           <t>Todos</t>
         </is>
       </c>
-      <c r="E12" s="7" t="n">
-        <v>46104</v>
-      </c>
-      <c r="F12" s="7" t="n">
-        <v>46110</v>
+      <c r="E12" s="19" t="n">
+        <v>46119</v>
+      </c>
+      <c r="F12" s="19" t="n">
+        <v>46121</v>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
@@ -1096,11 +1085,11 @@
           <t>Ricardo Silva</t>
         </is>
       </c>
-      <c r="E13" s="10" t="n">
-        <v>46104</v>
-      </c>
-      <c r="F13" s="10" t="n">
-        <v>46105</v>
+      <c r="E13" s="20" t="n">
+        <v>46119</v>
+      </c>
+      <c r="F13" s="20" t="n">
+        <v>46119</v>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
@@ -1142,15 +1131,15 @@
           <t>Alexandra Carrasco</t>
         </is>
       </c>
-      <c r="E14" s="13" t="n">
-        <v>46106</v>
-      </c>
-      <c r="F14" s="13" t="n">
-        <v>46107</v>
+      <c r="E14" s="21" t="n">
+        <v>46119</v>
+      </c>
+      <c r="F14" s="21" t="n">
+        <v>46120</v>
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="H14" s="11" t="n">
@@ -1188,11 +1177,11 @@
           <t>Lucas Rojas</t>
         </is>
       </c>
-      <c r="E15" s="10" t="n">
-        <v>46108</v>
-      </c>
-      <c r="F15" s="10" t="n">
-        <v>46108</v>
+      <c r="E15" s="20" t="n">
+        <v>46120</v>
+      </c>
+      <c r="F15" s="20" t="n">
+        <v>46120</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
@@ -1234,11 +1223,11 @@
           <t>Allan Gálvez</t>
         </is>
       </c>
-      <c r="E16" s="13" t="n">
-        <v>46109</v>
-      </c>
-      <c r="F16" s="13" t="n">
-        <v>46109</v>
+      <c r="E16" s="21" t="n">
+        <v>46121</v>
+      </c>
+      <c r="F16" s="21" t="n">
+        <v>46121</v>
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
@@ -1280,11 +1269,11 @@
           <t>Alejandro Dinamarca</t>
         </is>
       </c>
-      <c r="E17" s="16" t="n">
-        <v>46110</v>
-      </c>
-      <c r="F17" s="16" t="n">
-        <v>46110</v>
+      <c r="E17" s="22" t="n">
+        <v>46121</v>
+      </c>
+      <c r="F17" s="22" t="n">
+        <v>46121</v>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
@@ -1330,11 +1319,11 @@
           <t>Todos</t>
         </is>
       </c>
-      <c r="E18" s="7" t="n">
-        <v>46111</v>
-      </c>
-      <c r="F18" s="7" t="n">
-        <v>46132</v>
+      <c r="E18" s="19" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F18" s="19" t="n">
+        <v>46146</v>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
@@ -1376,11 +1365,11 @@
           <t>Allan Gálvez</t>
         </is>
       </c>
-      <c r="E19" s="10" t="n">
-        <v>46111</v>
-      </c>
-      <c r="F19" s="10" t="n">
-        <v>46114</v>
+      <c r="E19" s="20" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F19" s="20" t="n">
+        <v>46128</v>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
@@ -1422,11 +1411,11 @@
           <t>Alejandro Dinamarca</t>
         </is>
       </c>
-      <c r="E20" s="13" t="n">
-        <v>46115</v>
-      </c>
-      <c r="F20" s="13" t="n">
-        <v>46115</v>
+      <c r="E20" s="21" t="n">
+        <v>46129</v>
+      </c>
+      <c r="F20" s="21" t="n">
+        <v>46132</v>
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
@@ -1468,11 +1457,11 @@
           <t>Allan Gálvez</t>
         </is>
       </c>
-      <c r="E21" s="10" t="n">
-        <v>46116</v>
-      </c>
-      <c r="F21" s="10" t="n">
-        <v>46116</v>
+      <c r="E21" s="20" t="n">
+        <v>46133</v>
+      </c>
+      <c r="F21" s="20" t="n">
+        <v>46134</v>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
@@ -1514,11 +1503,11 @@
           <t>Alexandra Carrasco</t>
         </is>
       </c>
-      <c r="E22" s="13" t="n">
-        <v>46111</v>
-      </c>
-      <c r="F22" s="13" t="n">
-        <v>46113</v>
+      <c r="E22" s="21" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F22" s="21" t="n">
+        <v>46126</v>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
@@ -1560,11 +1549,11 @@
           <t>Lucas Rojas</t>
         </is>
       </c>
-      <c r="E23" s="10" t="n">
-        <v>46117</v>
-      </c>
-      <c r="F23" s="10" t="n">
-        <v>46118</v>
+      <c r="E23" s="20" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F23" s="20" t="n">
+        <v>46139</v>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
@@ -1606,11 +1595,11 @@
           <t>Ricardo Silva</t>
         </is>
       </c>
-      <c r="E24" s="13" t="n">
-        <v>46119</v>
-      </c>
-      <c r="F24" s="13" t="n">
-        <v>46124</v>
+      <c r="E24" s="21" t="n">
+        <v>46140</v>
+      </c>
+      <c r="F24" s="21" t="n">
+        <v>46143</v>
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
@@ -1652,11 +1641,11 @@
           <t>Lucas Rojas</t>
         </is>
       </c>
-      <c r="E25" s="10" t="n">
-        <v>46125</v>
-      </c>
-      <c r="F25" s="10" t="n">
-        <v>46127</v>
+      <c r="E25" s="20" t="n">
+        <v>46144</v>
+      </c>
+      <c r="F25" s="20" t="n">
+        <v>46145</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
@@ -1698,11 +1687,11 @@
           <t>Alexandra Carrasco</t>
         </is>
       </c>
-      <c r="E26" s="13" t="n">
-        <v>46128</v>
-      </c>
-      <c r="F26" s="13" t="n">
-        <v>46129</v>
+      <c r="E26" s="21" t="n">
+        <v>46145</v>
+      </c>
+      <c r="F26" s="21" t="n">
+        <v>46146</v>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
@@ -1748,12 +1737,12 @@
           <t>Todos</t>
         </is>
       </c>
-      <c r="E27" s="7" t="n">
-        <v>46130</v>
-      </c>
-      <c r="F27" s="7" t="n">
+      <c r="E27" s="19" t="n">
         <v>46148</v>
       </c>
+      <c r="F27" s="19" t="n">
+        <v>46174</v>
+      </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
           <t>4.8</t>
@@ -1769,7 +1758,7 @@
         <v>0</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
@@ -1794,11 +1783,11 @@
           <t>Ricardo Silva</t>
         </is>
       </c>
-      <c r="E28" s="13" t="n">
-        <v>46130</v>
-      </c>
-      <c r="F28" s="13" t="n">
-        <v>46132</v>
+      <c r="E28" s="21" t="n">
+        <v>46148</v>
+      </c>
+      <c r="F28" s="21" t="n">
+        <v>46153</v>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
@@ -1840,11 +1829,11 @@
           <t>Alexandra Carrasco</t>
         </is>
       </c>
-      <c r="E29" s="10" t="n">
-        <v>46133</v>
-      </c>
-      <c r="F29" s="10" t="n">
-        <v>46134</v>
+      <c r="E29" s="20" t="n">
+        <v>46154</v>
+      </c>
+      <c r="F29" s="20" t="n">
+        <v>46157</v>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
@@ -1886,11 +1875,11 @@
           <t>Alejandro Dinamarca</t>
         </is>
       </c>
-      <c r="E30" s="13" t="n">
-        <v>46135</v>
-      </c>
-      <c r="F30" s="13" t="n">
-        <v>46140</v>
+      <c r="E30" s="21" t="n">
+        <v>46158</v>
+      </c>
+      <c r="F30" s="21" t="n">
+        <v>46164</v>
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
@@ -1932,11 +1921,11 @@
           <t>Lucas Rojas</t>
         </is>
       </c>
-      <c r="E31" s="10" t="n">
-        <v>46141</v>
-      </c>
-      <c r="F31" s="10" t="n">
-        <v>46142</v>
+      <c r="E31" s="20" t="n">
+        <v>46165</v>
+      </c>
+      <c r="F31" s="20" t="n">
+        <v>46167</v>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
@@ -1978,11 +1967,11 @@
           <t>Allan Gálvez</t>
         </is>
       </c>
-      <c r="E32" s="13" t="n">
-        <v>46143</v>
-      </c>
-      <c r="F32" s="13" t="n">
-        <v>46144</v>
+      <c r="E32" s="21" t="n">
+        <v>46168</v>
+      </c>
+      <c r="F32" s="21" t="n">
+        <v>46169</v>
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
@@ -2024,11 +2013,11 @@
           <t>Ricardo Silva</t>
         </is>
       </c>
-      <c r="E33" s="10" t="n">
-        <v>46145</v>
-      </c>
-      <c r="F33" s="10" t="n">
-        <v>46147</v>
+      <c r="E33" s="20" t="n">
+        <v>46170</v>
+      </c>
+      <c r="F33" s="20" t="n">
+        <v>46172</v>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
@@ -2070,11 +2059,11 @@
           <t>Alejandro Dinamarca</t>
         </is>
       </c>
-      <c r="E34" s="16" t="n">
-        <v>46148</v>
-      </c>
-      <c r="F34" s="16" t="n">
-        <v>46148</v>
+      <c r="E34" s="22" t="n">
+        <v>46174</v>
+      </c>
+      <c r="F34" s="22" t="n">
+        <v>46174</v>
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
@@ -2120,11 +2109,11 @@
           <t>Todos</t>
         </is>
       </c>
-      <c r="E35" s="7" t="n">
-        <v>46149</v>
-      </c>
-      <c r="F35" s="7" t="n">
-        <v>46157</v>
+      <c r="E35" s="19" t="n">
+        <v>46175</v>
+      </c>
+      <c r="F35" s="19" t="n">
+        <v>46185</v>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
@@ -2141,7 +2130,7 @@
         <v>0</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L35" s="6" t="inlineStr">
         <is>
@@ -2166,11 +2155,11 @@
           <t>Alejandro Dinamarca</t>
         </is>
       </c>
-      <c r="E36" s="13" t="n">
-        <v>46149</v>
-      </c>
-      <c r="F36" s="13" t="n">
-        <v>46150</v>
+      <c r="E36" s="21" t="n">
+        <v>46175</v>
+      </c>
+      <c r="F36" s="21" t="n">
+        <v>46177</v>
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
@@ -2212,11 +2201,11 @@
           <t>Alexandra Carrasco</t>
         </is>
       </c>
-      <c r="E37" s="10" t="n">
-        <v>46151</v>
-      </c>
-      <c r="F37" s="10" t="n">
-        <v>46155</v>
+      <c r="E37" s="20" t="n">
+        <v>46178</v>
+      </c>
+      <c r="F37" s="20" t="n">
+        <v>46183</v>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
@@ -2258,11 +2247,11 @@
           <t>Lucas Rojas</t>
         </is>
       </c>
-      <c r="E38" s="13" t="n">
-        <v>46155</v>
-      </c>
-      <c r="F38" s="13" t="n">
-        <v>46156</v>
+      <c r="E38" s="21" t="n">
+        <v>46184</v>
+      </c>
+      <c r="F38" s="21" t="n">
+        <v>46185</v>
       </c>
       <c r="G38" s="11" t="inlineStr">
         <is>
@@ -2308,11 +2297,11 @@
           <t>Todos</t>
         </is>
       </c>
-      <c r="E39" s="7" t="n">
-        <v>46157</v>
-      </c>
-      <c r="F39" s="7" t="n">
-        <v>46163</v>
+      <c r="E39" s="19" t="n">
+        <v>46186</v>
+      </c>
+      <c r="F39" s="19" t="n">
+        <v>46192</v>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
@@ -2354,15 +2343,15 @@
           <t>Allan Gálvez</t>
         </is>
       </c>
-      <c r="E40" s="13" t="n">
-        <v>46157</v>
-      </c>
-      <c r="F40" s="13" t="n">
-        <v>46161</v>
+      <c r="E40" s="21" t="n">
+        <v>46186</v>
+      </c>
+      <c r="F40" s="21" t="n">
+        <v>46189</v>
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="H40" s="11" t="n">
@@ -2400,11 +2389,11 @@
           <t>Ricardo Silva</t>
         </is>
       </c>
-      <c r="E41" s="10" t="n">
-        <v>46161</v>
-      </c>
-      <c r="F41" s="10" t="n">
-        <v>46163</v>
+      <c r="E41" s="20" t="n">
+        <v>46189</v>
+      </c>
+      <c r="F41" s="20" t="n">
+        <v>46191</v>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
@@ -2450,11 +2439,11 @@
           <t>Todos</t>
         </is>
       </c>
-      <c r="E42" s="7" t="n">
-        <v>46164</v>
-      </c>
-      <c r="F42" s="7" t="n">
-        <v>46169</v>
+      <c r="E42" s="19" t="n">
+        <v>46193</v>
+      </c>
+      <c r="F42" s="19" t="n">
+        <v>46197</v>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
@@ -2496,11 +2485,11 @@
           <t>Ricardo Silva</t>
         </is>
       </c>
-      <c r="E43" s="10" t="n">
-        <v>46164</v>
-      </c>
-      <c r="F43" s="10" t="n">
-        <v>46166</v>
+      <c r="E43" s="20" t="n">
+        <v>46193</v>
+      </c>
+      <c r="F43" s="20" t="n">
+        <v>46195</v>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
@@ -2517,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="K43" s="8" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L43" s="9" t="inlineStr">
         <is>
@@ -2542,11 +2531,11 @@
           <t>Alejandro Dinamarca</t>
         </is>
       </c>
-      <c r="E44" s="16" t="n">
-        <v>46169</v>
-      </c>
-      <c r="F44" s="16" t="n">
-        <v>46169</v>
+      <c r="E44" s="22" t="n">
+        <v>46197</v>
+      </c>
+      <c r="F44" s="22" t="n">
+        <v>46197</v>
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
@@ -2587,7 +2576,7 @@
       <c r="I45" s="17" t="n"/>
       <c r="J45" s="17" t="n"/>
       <c r="K45" s="18" t="n">
-        <v>552</v>
+        <v>576</v>
       </c>
       <c r="L45" s="17" t="n"/>
     </row>
